--- a/Input/MasterConfig.xlsx
+++ b/Input/MasterConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ashimnayak/Desktop/HYBRID-SELENIUM-FRAMEWORK/Input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ACBD9FC-3BC6-2345-AEFA-FB34D440AF6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DDAB105-47F2-FD49-8614-9754CC2259AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="600" windowWidth="28040" windowHeight="16060" xr2:uid="{F2199F72-D956-A54E-BE79-37BB8B45A2E8}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
   <si>
     <t>ModuleName</t>
   </si>
@@ -95,6 +95,9 @@
   </si>
   <si>
     <t>API Module — data-driven REST API tests via JSONPlaceholder</t>
+  </si>
+  <si>
+    <t>No</t>
   </si>
 </sst>
 </file>
@@ -528,7 +531,7 @@
         <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
         <v>17</v>

--- a/Input/MasterConfig.xlsx
+++ b/Input/MasterConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ashimnayak/Desktop/HYBRID-SELENIUM-FRAMEWORK/Input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DDAB105-47F2-FD49-8614-9754CC2259AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3B7BC86-8220-0B41-915A-BDE77A913B33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="600" windowWidth="28040" windowHeight="16060" xr2:uid="{F2199F72-D956-A54E-BE79-37BB8B45A2E8}"/>
   </bookViews>
@@ -511,7 +511,7 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s">
         <v>13</v>

--- a/Input/MasterConfig.xlsx
+++ b/Input/MasterConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ashimnayak/Desktop/HYBRID-SELENIUM-FRAMEWORK/Input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3B7BC86-8220-0B41-915A-BDE77A913B33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C29E0CC8-EE70-9448-A12C-7343D5B5E12D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="600" windowWidth="28040" windowHeight="16060" xr2:uid="{F2199F72-D956-A54E-BE79-37BB8B45A2E8}"/>
   </bookViews>
@@ -531,7 +531,7 @@
         <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="C4" t="s">
         <v>17</v>

--- a/Input/MasterConfig.xlsx
+++ b/Input/MasterConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ashimnayak/Desktop/HYBRID-SELENIUM-FRAMEWORK/Input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C29E0CC8-EE70-9448-A12C-7343D5B5E12D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE8077D7-B2A6-F141-B057-911EC9DB3DDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="600" windowWidth="28040" windowHeight="16060" xr2:uid="{F2199F72-D956-A54E-BE79-37BB8B45A2E8}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="20">
   <si>
     <t>ModuleName</t>
   </si>
@@ -95,9 +95,6 @@
   </si>
   <si>
     <t>API Module — data-driven REST API tests via JSONPlaceholder</t>
-  </si>
-  <si>
-    <t>No</t>
   </si>
 </sst>
 </file>
@@ -511,7 +508,7 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
         <v>13</v>

--- a/Input/MasterConfig.xlsx
+++ b/Input/MasterConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ashimnayak/Desktop/HYBRID-SELENIUM-FRAMEWORK/Input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE8077D7-B2A6-F141-B057-911EC9DB3DDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E3AAF73-885F-4B46-A9D9-AD7ECEA4437B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="600" windowWidth="28040" windowHeight="16060" xr2:uid="{F2199F72-D956-A54E-BE79-37BB8B45A2E8}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
   <si>
     <t>ModuleName</t>
   </si>
@@ -95,6 +95,9 @@
   </si>
   <si>
     <t>API Module — data-driven REST API tests via JSONPlaceholder</t>
+  </si>
+  <si>
+    <t>No</t>
   </si>
 </sst>
 </file>
@@ -488,7 +491,7 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="C2" t="s">
         <v>8</v>

--- a/Input/MasterConfig.xlsx
+++ b/Input/MasterConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ashimnayak/Desktop/HYBRID-SELENIUM-FRAMEWORK/Input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E3AAF73-885F-4B46-A9D9-AD7ECEA4437B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3130F8DB-BD33-8A4E-AB08-7C650244EE0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="600" windowWidth="28040" windowHeight="16060" xr2:uid="{F2199F72-D956-A54E-BE79-37BB8B45A2E8}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="20">
   <si>
     <t>ModuleName</t>
   </si>
@@ -95,9 +95,6 @@
   </si>
   <si>
     <t>API Module — data-driven REST API tests via JSONPlaceholder</t>
-  </si>
-  <si>
-    <t>No</t>
   </si>
 </sst>
 </file>
@@ -491,7 +488,7 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="C2" t="s">
         <v>8</v>

--- a/Input/MasterConfig.xlsx
+++ b/Input/MasterConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ashimnayak/Desktop/HYBRID-SELENIUM-FRAMEWORK/Input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3130F8DB-BD33-8A4E-AB08-7C650244EE0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E5070CE-9195-834B-B8DC-E050203CD312}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="600" windowWidth="28040" windowHeight="16060" xr2:uid="{F2199F72-D956-A54E-BE79-37BB8B45A2E8}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="21">
   <si>
     <t>ModuleName</t>
   </si>
@@ -95,6 +95,9 @@
   </si>
   <si>
     <t>API Module — data-driven REST API tests via JSONPlaceholder</t>
+  </si>
+  <si>
+    <t>No</t>
   </si>
 </sst>
 </file>
@@ -528,7 +531,7 @@
         <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
         <v>17</v>

--- a/Input/MasterConfig.xlsx
+++ b/Input/MasterConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ashimnayak/Desktop/HYBRID-SELENIUM-FRAMEWORK/Input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E5070CE-9195-834B-B8DC-E050203CD312}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E988472-00C2-8B45-B50B-4C7391DF5EF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="600" windowWidth="28040" windowHeight="16060" xr2:uid="{F2199F72-D956-A54E-BE79-37BB8B45A2E8}"/>
   </bookViews>

--- a/Input/MasterConfig.xlsx
+++ b/Input/MasterConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ashimnayak/Desktop/HYBRID-SELENIUM-FRAMEWORK/Input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E988472-00C2-8B45-B50B-4C7391DF5EF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15E019A1-C98D-3549-B268-FF70643DF22D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="600" windowWidth="28040" windowHeight="16060" xr2:uid="{F2199F72-D956-A54E-BE79-37BB8B45A2E8}"/>
   </bookViews>
@@ -491,7 +491,7 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="C2" t="s">
         <v>8</v>
@@ -511,7 +511,7 @@
         <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s">
         <v>13</v>
@@ -531,7 +531,7 @@
         <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="C4" t="s">
         <v>17</v>
